--- a/agent-improve/evals/define/judge_labelling_corrections.xlsx
+++ b/agent-improve/evals/define/judge_labelling_corrections.xlsx
@@ -444,9 +444,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -461,9 +459,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -614,7 +610,11 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="2" t="n"/>
     </row>
@@ -663,9 +663,17 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="2" t="n"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>re-asks to confirm the stored SIPOC instead of moving on (G-158 pattern)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -709,7 +717,11 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="2" t="n"/>
     </row>
@@ -755,7 +767,11 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="2" t="n"/>
     </row>
@@ -801,16 +817,24 @@
           <t>coherence</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="n"/>
-      <c r="L6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>terse; doesn't explain the review step</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="J2:J6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"right,wrong"</formula1>
     </dataValidation>
   </dataValidations>
